--- a/output/yearly_total_coral_cover_iteration_71_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_71_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.259195923225082</v>
+        <v>1.247277506095526</v>
       </c>
       <c r="C3" t="n">
-        <v>4.616518262882038</v>
+        <v>4.64035509714115</v>
       </c>
       <c r="D3" t="n">
-        <v>6.063484991119354</v>
+        <v>6.068315189824249</v>
       </c>
       <c r="E3" t="n">
-        <v>11.93919917722648</v>
+        <v>11.95594779306093</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.385077417410844</v>
+        <v>1.372321635540442</v>
       </c>
       <c r="C4" t="n">
-        <v>5.091023442494212</v>
+        <v>5.170392488441432</v>
       </c>
       <c r="D4" t="n">
-        <v>6.253503409538698</v>
+        <v>6.458580348750317</v>
       </c>
       <c r="E4" t="n">
-        <v>12.72960426944375</v>
+        <v>13.00129447273219</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.551696317489314</v>
+        <v>1.538574247036109</v>
       </c>
       <c r="C5" t="n">
-        <v>5.740407919808722</v>
+        <v>5.835006580797941</v>
       </c>
       <c r="D5" t="n">
-        <v>6.538340479416915</v>
+        <v>6.773830537972761</v>
       </c>
       <c r="E5" t="n">
-        <v>13.83044471671495</v>
+        <v>14.14741136580681</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.743962622678904</v>
+        <v>1.734190312562864</v>
       </c>
       <c r="C6" t="n">
-        <v>6.554105475665402</v>
+        <v>6.67985129576247</v>
       </c>
       <c r="D6" t="n">
-        <v>6.819924175797272</v>
+        <v>7.163518902415244</v>
       </c>
       <c r="E6" t="n">
-        <v>15.11799227414158</v>
+        <v>15.57756051074058</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>1.958769179705995</v>
+        <v>1.955914592385742</v>
       </c>
       <c r="C7" t="n">
-        <v>7.53602902150858</v>
+        <v>7.734827824135923</v>
       </c>
       <c r="D7" t="n">
-        <v>7.177080487043965</v>
+        <v>7.56517379222114</v>
       </c>
       <c r="E7" t="n">
-        <v>16.67187868825854</v>
+        <v>17.25591620874281</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.19131731576285</v>
+        <v>1.180633011282275</v>
       </c>
       <c r="C8" t="n">
-        <v>5.23898482785847</v>
+        <v>5.497580764100619</v>
       </c>
       <c r="D8" t="n">
-        <v>5.508799299841642</v>
+        <v>5.921489149304932</v>
       </c>
       <c r="E8" t="n">
-        <v>11.93910144346296</v>
+        <v>12.59970292468783</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.497103214990691</v>
+        <v>1.462352485713072</v>
       </c>
       <c r="C9" t="n">
-        <v>6.47937107461781</v>
+        <v>6.958491617373686</v>
       </c>
       <c r="D9" t="n">
-        <v>5.998251160177655</v>
+        <v>6.558460008089569</v>
       </c>
       <c r="E9" t="n">
-        <v>13.97472544978616</v>
+        <v>14.97930411117633</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.82875367575457</v>
+        <v>1.738081580329487</v>
       </c>
       <c r="C10" t="n">
-        <v>7.885487270366993</v>
+        <v>8.617700648670384</v>
       </c>
       <c r="D10" t="n">
-        <v>6.528939532175473</v>
+        <v>7.151684427881095</v>
       </c>
       <c r="E10" t="n">
-        <v>16.24318047829703</v>
+        <v>17.50746665688097</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.154471119205998</v>
+        <v>2.016067840733172</v>
       </c>
       <c r="C11" t="n">
-        <v>9.423022305508978</v>
+        <v>10.39000096327933</v>
       </c>
       <c r="D11" t="n">
-        <v>6.980863865787373</v>
+        <v>7.74559653010277</v>
       </c>
       <c r="E11" t="n">
-        <v>18.55835729050235</v>
+        <v>20.15166533411526</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.484336199356089</v>
+        <v>2.27504092524485</v>
       </c>
       <c r="C12" t="n">
-        <v>11.10883159981184</v>
+        <v>12.17818524880257</v>
       </c>
       <c r="D12" t="n">
-        <v>7.46477520950191</v>
+        <v>8.257326409531634</v>
       </c>
       <c r="E12" t="n">
-        <v>21.05794300866984</v>
+        <v>22.71055258357905</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.808902194022425</v>
+        <v>2.508942883794364</v>
       </c>
       <c r="C13" t="n">
-        <v>12.81204449303403</v>
+        <v>13.94044326398964</v>
       </c>
       <c r="D13" t="n">
-        <v>7.875965061884391</v>
+        <v>8.795058274945692</v>
       </c>
       <c r="E13" t="n">
-        <v>23.49691174894084</v>
+        <v>25.2444444227297</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.616162888208142</v>
+        <v>1.446958671381204</v>
       </c>
       <c r="C14" t="n">
-        <v>8.991198904665819</v>
+        <v>9.553112020668523</v>
       </c>
       <c r="D14" t="n">
-        <v>6.006685883755515</v>
+        <v>6.659852448867961</v>
       </c>
       <c r="E14" t="n">
-        <v>16.61404767662948</v>
+        <v>17.65992314091769</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.660439709669673</v>
+        <v>1.443532371893383</v>
       </c>
       <c r="C15" t="n">
-        <v>9.79124474381063</v>
+        <v>10.36074676956716</v>
       </c>
       <c r="D15" t="n">
-        <v>5.994522029699897</v>
+        <v>6.70686834642434</v>
       </c>
       <c r="E15" t="n">
-        <v>17.4462064831802</v>
+        <v>18.51114748788488</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.922527076795401</v>
+        <v>1.636995574492259</v>
       </c>
       <c r="C16" t="n">
-        <v>11.58706746189594</v>
+        <v>12.19336539160764</v>
       </c>
       <c r="D16" t="n">
-        <v>6.40706223250145</v>
+        <v>7.29784119447275</v>
       </c>
       <c r="E16" t="n">
-        <v>19.91665677119279</v>
+        <v>21.12820216057265</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.541540245208342</v>
+        <v>1.287611201504904</v>
       </c>
       <c r="C17" t="n">
-        <v>10.66984021677223</v>
+        <v>11.1630408109547</v>
       </c>
       <c r="D17" t="n">
-        <v>5.913900908227149</v>
+        <v>6.805416180976635</v>
       </c>
       <c r="E17" t="n">
-        <v>18.12528137020772</v>
+        <v>19.25606819343623</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.757249850785451</v>
+        <v>1.43815239447411</v>
       </c>
       <c r="C18" t="n">
-        <v>12.45434338382757</v>
+        <v>12.9532675671258</v>
       </c>
       <c r="D18" t="n">
-        <v>6.316839618481167</v>
+        <v>7.254752287733357</v>
       </c>
       <c r="E18" t="n">
-        <v>20.52843285309419</v>
+        <v>21.64617224933327</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.761206294033565</v>
+        <v>1.414610084526272</v>
       </c>
       <c r="C19" t="n">
-        <v>13.30717779702973</v>
+        <v>13.80987189151227</v>
       </c>
       <c r="D19" t="n">
-        <v>6.378728993756885</v>
+        <v>7.372836901600164</v>
       </c>
       <c r="E19" t="n">
-        <v>21.44711308482018</v>
+        <v>22.5973188776387</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1.958233240798858</v>
+        <v>1.545202164145183</v>
       </c>
       <c r="C20" t="n">
-        <v>15.30448459645761</v>
+        <v>15.85036577244996</v>
       </c>
       <c r="D20" t="n">
-        <v>6.802353128139384</v>
+        <v>7.824970989313991</v>
       </c>
       <c r="E20" t="n">
-        <v>24.06507096539585</v>
+        <v>25.22053892590914</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.162084940039907</v>
+        <v>0.9043172628128646</v>
       </c>
       <c r="C21" t="n">
-        <v>11.21753762601744</v>
+        <v>11.60066466759976</v>
       </c>
       <c r="D21" t="n">
-        <v>5.667776758772474</v>
+        <v>6.552753591811676</v>
       </c>
       <c r="E21" t="n">
-        <v>18.04739932482982</v>
+        <v>19.0577355222243</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_total_coral_cover_iteration_71_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_71_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.247277506095526</v>
+        <v>1.256771006395593</v>
       </c>
       <c r="C3" t="n">
-        <v>4.64035509714115</v>
+        <v>4.617077859073458</v>
       </c>
       <c r="D3" t="n">
-        <v>6.068315189824249</v>
+        <v>6.166813936991331</v>
       </c>
       <c r="E3" t="n">
-        <v>11.95594779306093</v>
+        <v>12.04066280246038</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.372321635540442</v>
+        <v>1.382556550187518</v>
       </c>
       <c r="C4" t="n">
-        <v>5.170392488441432</v>
+        <v>5.089322226765292</v>
       </c>
       <c r="D4" t="n">
-        <v>6.458580348750317</v>
+        <v>6.576898872491404</v>
       </c>
       <c r="E4" t="n">
-        <v>13.00129447273219</v>
+        <v>13.04877764944422</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.538574247036109</v>
+        <v>1.552990126372057</v>
       </c>
       <c r="C5" t="n">
-        <v>5.835006580797941</v>
+        <v>5.671893476855421</v>
       </c>
       <c r="D5" t="n">
-        <v>6.773830537972761</v>
+        <v>6.957284335803568</v>
       </c>
       <c r="E5" t="n">
-        <v>14.14741136580681</v>
+        <v>14.18216793903104</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.734190312562864</v>
+        <v>1.76071217971809</v>
       </c>
       <c r="C6" t="n">
-        <v>6.67985129576247</v>
+        <v>6.393216512756095</v>
       </c>
       <c r="D6" t="n">
-        <v>7.163518902415244</v>
+        <v>7.3317622219079</v>
       </c>
       <c r="E6" t="n">
-        <v>15.57756051074058</v>
+        <v>15.48569091438209</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>1.955914592385742</v>
+        <v>1.994253047523703</v>
       </c>
       <c r="C7" t="n">
-        <v>7.734827824135923</v>
+        <v>7.232141138265705</v>
       </c>
       <c r="D7" t="n">
-        <v>7.56517379222114</v>
+        <v>7.829385409309428</v>
       </c>
       <c r="E7" t="n">
-        <v>17.25591620874281</v>
+        <v>17.05577959509884</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.180633011282275</v>
+        <v>1.222482838604203</v>
       </c>
       <c r="C8" t="n">
-        <v>5.497580764100619</v>
+        <v>4.880732888293926</v>
       </c>
       <c r="D8" t="n">
-        <v>5.921489149304932</v>
+        <v>6.207840339806929</v>
       </c>
       <c r="E8" t="n">
-        <v>12.59970292468783</v>
+        <v>12.31105606670506</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.462352485713072</v>
+        <v>1.519857767757714</v>
       </c>
       <c r="C9" t="n">
-        <v>6.958491617373686</v>
+        <v>5.946512850809187</v>
       </c>
       <c r="D9" t="n">
-        <v>6.558460008089569</v>
+        <v>6.876905387063505</v>
       </c>
       <c r="E9" t="n">
-        <v>14.97930411117633</v>
+        <v>14.34327600563041</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.738081580329487</v>
+        <v>1.836786289993292</v>
       </c>
       <c r="C10" t="n">
-        <v>8.617700648670384</v>
+        <v>7.163683364801749</v>
       </c>
       <c r="D10" t="n">
-        <v>7.151684427881095</v>
+        <v>7.502402571605571</v>
       </c>
       <c r="E10" t="n">
-        <v>17.50746665688097</v>
+        <v>16.50287222640061</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.016067840733172</v>
+        <v>2.159631952175056</v>
       </c>
       <c r="C11" t="n">
-        <v>10.39000096327933</v>
+        <v>8.498314329919015</v>
       </c>
       <c r="D11" t="n">
-        <v>7.74559653010277</v>
+        <v>8.107746767895206</v>
       </c>
       <c r="E11" t="n">
-        <v>20.15166533411526</v>
+        <v>18.76569304998928</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.27504092524485</v>
+        <v>2.483979654611833</v>
       </c>
       <c r="C12" t="n">
-        <v>12.17818524880257</v>
+        <v>9.935159466761558</v>
       </c>
       <c r="D12" t="n">
-        <v>8.257326409531634</v>
+        <v>8.831431504100387</v>
       </c>
       <c r="E12" t="n">
-        <v>22.71055258357905</v>
+        <v>21.25057062547378</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.508942883794364</v>
+        <v>2.796796231556446</v>
       </c>
       <c r="C13" t="n">
-        <v>13.94044326398964</v>
+        <v>11.41684763724479</v>
       </c>
       <c r="D13" t="n">
-        <v>8.795058274945692</v>
+        <v>9.408487389717111</v>
       </c>
       <c r="E13" t="n">
-        <v>25.2444444227297</v>
+        <v>23.62213125851835</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.446958671381204</v>
+        <v>1.615544387154466</v>
       </c>
       <c r="C14" t="n">
-        <v>9.553112020668523</v>
+        <v>8.046600533547707</v>
       </c>
       <c r="D14" t="n">
-        <v>6.659852448867961</v>
+        <v>7.10094187490901</v>
       </c>
       <c r="E14" t="n">
-        <v>17.65992314091769</v>
+        <v>16.76308679561118</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.443532371893383</v>
+        <v>1.649669937354086</v>
       </c>
       <c r="C15" t="n">
-        <v>10.36074676956716</v>
+        <v>8.68996925657177</v>
       </c>
       <c r="D15" t="n">
-        <v>6.70686834642434</v>
+        <v>7.202582214729683</v>
       </c>
       <c r="E15" t="n">
-        <v>18.51114748788488</v>
+        <v>17.54222140865554</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.636995574492259</v>
+        <v>1.912729234707018</v>
       </c>
       <c r="C16" t="n">
-        <v>12.19336539160764</v>
+        <v>10.25702512461348</v>
       </c>
       <c r="D16" t="n">
-        <v>7.29784119447275</v>
+        <v>7.791944996543127</v>
       </c>
       <c r="E16" t="n">
-        <v>21.12820216057265</v>
+        <v>19.96169935586363</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.287611201504904</v>
+        <v>1.536199537697239</v>
       </c>
       <c r="C17" t="n">
-        <v>11.1630408109547</v>
+        <v>9.464342393250526</v>
       </c>
       <c r="D17" t="n">
-        <v>6.805416180976635</v>
+        <v>7.30113986675902</v>
       </c>
       <c r="E17" t="n">
-        <v>19.25606819343623</v>
+        <v>18.30168179770678</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.43815239447411</v>
+        <v>1.753970813453267</v>
       </c>
       <c r="C18" t="n">
-        <v>12.9532675671258</v>
+        <v>11.00445910428771</v>
       </c>
       <c r="D18" t="n">
-        <v>7.254752287733357</v>
+        <v>7.815497123968009</v>
       </c>
       <c r="E18" t="n">
-        <v>21.64617224933327</v>
+        <v>20.57392704170899</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.414610084526272</v>
+        <v>1.760479800732423</v>
       </c>
       <c r="C19" t="n">
-        <v>13.80987189151227</v>
+        <v>11.73501684092593</v>
       </c>
       <c r="D19" t="n">
-        <v>7.372836901600164</v>
+        <v>7.964919124554373</v>
       </c>
       <c r="E19" t="n">
-        <v>22.5973188776387</v>
+        <v>21.46041576621273</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1.545202164145183</v>
+        <v>1.962818002577691</v>
       </c>
       <c r="C20" t="n">
-        <v>15.85036577244996</v>
+        <v>13.44759717116815</v>
       </c>
       <c r="D20" t="n">
-        <v>7.824970989313991</v>
+        <v>8.469753429032169</v>
       </c>
       <c r="E20" t="n">
-        <v>25.22053892590914</v>
+        <v>23.88016860277801</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>0.9043172628128646</v>
+        <v>1.169477500252885</v>
       </c>
       <c r="C21" t="n">
-        <v>11.60066466759976</v>
+        <v>9.847096370705231</v>
       </c>
       <c r="D21" t="n">
-        <v>6.552753591811676</v>
+        <v>7.095561897489739</v>
       </c>
       <c r="E21" t="n">
-        <v>19.0577355222243</v>
+        <v>18.11213576844785</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_total_coral_cover_iteration_71_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_71_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.256771006395593</v>
+        <v>2.607737408857992</v>
       </c>
       <c r="C3" t="n">
-        <v>4.617077859073458</v>
+        <v>7.821345509641826</v>
       </c>
       <c r="D3" t="n">
-        <v>6.166813936991331</v>
+        <v>8.166293018706899</v>
       </c>
       <c r="E3" t="n">
-        <v>12.04066280246038</v>
+        <v>18.59537593720672</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.382556550187518</v>
+        <v>1.104946552848944</v>
       </c>
       <c r="C4" t="n">
-        <v>5.089322226765292</v>
+        <v>4.805100481117321</v>
       </c>
       <c r="D4" t="n">
-        <v>6.576898872491404</v>
+        <v>5.828448888830784</v>
       </c>
       <c r="E4" t="n">
-        <v>13.04877764944422</v>
+        <v>11.73849592279705</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.552990126372057</v>
+        <v>1.216530547139786</v>
       </c>
       <c r="C5" t="n">
-        <v>5.671893476855421</v>
+        <v>5.819967939289182</v>
       </c>
       <c r="D5" t="n">
-        <v>6.957284335803568</v>
+        <v>6.173870915823878</v>
       </c>
       <c r="E5" t="n">
-        <v>14.18216793903104</v>
+        <v>13.21036940225285</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.76071217971809</v>
+        <v>1.331769062952559</v>
       </c>
       <c r="C6" t="n">
-        <v>6.393216512756095</v>
+        <v>7.123170595653148</v>
       </c>
       <c r="D6" t="n">
-        <v>7.3317622219079</v>
+        <v>6.501218190608519</v>
       </c>
       <c r="E6" t="n">
-        <v>15.48569091438209</v>
+        <v>14.95615784921423</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>1.994253047523703</v>
+        <v>1.451578300536758</v>
       </c>
       <c r="C7" t="n">
-        <v>7.232141138265705</v>
+        <v>8.607604569704266</v>
       </c>
       <c r="D7" t="n">
-        <v>7.829385409309428</v>
+        <v>6.908983436414131</v>
       </c>
       <c r="E7" t="n">
-        <v>17.05577959509884</v>
+        <v>16.96816630665516</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.222482838604203</v>
+        <v>1.577498784340975</v>
       </c>
       <c r="C8" t="n">
-        <v>4.880732888293926</v>
+        <v>10.27785122349968</v>
       </c>
       <c r="D8" t="n">
-        <v>6.207840339806929</v>
+        <v>7.27390301125547</v>
       </c>
       <c r="E8" t="n">
-        <v>12.31105606670506</v>
+        <v>19.12925301909613</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.519857767757714</v>
+        <v>1.687276888856311</v>
       </c>
       <c r="C9" t="n">
-        <v>5.946512850809187</v>
+        <v>12.09895709267513</v>
       </c>
       <c r="D9" t="n">
-        <v>6.876905387063505</v>
+        <v>7.6847291523435</v>
       </c>
       <c r="E9" t="n">
-        <v>14.34327600563041</v>
+        <v>21.47096313387494</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.836786289993292</v>
+        <v>1.05418104986614</v>
       </c>
       <c r="C10" t="n">
-        <v>7.163683364801749</v>
+        <v>8.597331543199042</v>
       </c>
       <c r="D10" t="n">
-        <v>7.502402571605571</v>
+        <v>6.028195975955563</v>
       </c>
       <c r="E10" t="n">
-        <v>16.50287222640061</v>
+        <v>15.67970856902074</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.159631952175056</v>
+        <v>0.9807659565425635</v>
       </c>
       <c r="C11" t="n">
-        <v>8.498314329919015</v>
+        <v>9.526437935544138</v>
       </c>
       <c r="D11" t="n">
-        <v>8.107746767895206</v>
+        <v>5.863409623797735</v>
       </c>
       <c r="E11" t="n">
-        <v>18.76569304998928</v>
+        <v>16.37061351588444</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.483979654611833</v>
+        <v>1.045198058372282</v>
       </c>
       <c r="C12" t="n">
-        <v>9.935159466761558</v>
+        <v>11.52065222970364</v>
       </c>
       <c r="D12" t="n">
-        <v>8.831431504100387</v>
+        <v>6.263285281214503</v>
       </c>
       <c r="E12" t="n">
-        <v>21.25057062547378</v>
+        <v>18.82913556929043</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.796796231556446</v>
+        <v>0.8202796593293374</v>
       </c>
       <c r="C13" t="n">
-        <v>11.41684763724479</v>
+        <v>11.11433630734702</v>
       </c>
       <c r="D13" t="n">
-        <v>9.408487389717111</v>
+        <v>5.699801368885005</v>
       </c>
       <c r="E13" t="n">
-        <v>23.62213125851835</v>
+        <v>17.63441733556136</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.615544387154466</v>
+        <v>0.8746586646675684</v>
       </c>
       <c r="C14" t="n">
-        <v>8.046600533547707</v>
+        <v>13.15876699657874</v>
       </c>
       <c r="D14" t="n">
-        <v>7.10094187490901</v>
+        <v>6.008472664577243</v>
       </c>
       <c r="E14" t="n">
-        <v>16.76308679561118</v>
+        <v>20.04189832582355</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.649669937354086</v>
+        <v>0.8328263949896118</v>
       </c>
       <c r="C15" t="n">
-        <v>8.68996925657177</v>
+        <v>14.31254635104072</v>
       </c>
       <c r="D15" t="n">
-        <v>7.202582214729683</v>
+        <v>6.021107757530901</v>
       </c>
       <c r="E15" t="n">
-        <v>17.54222140865554</v>
+        <v>21.16648050356124</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.912729234707018</v>
+        <v>0.893419863295725</v>
       </c>
       <c r="C16" t="n">
-        <v>10.25702512461348</v>
+        <v>16.62545558495282</v>
       </c>
       <c r="D16" t="n">
-        <v>7.791944996543127</v>
+        <v>6.378758446188013</v>
       </c>
       <c r="E16" t="n">
-        <v>19.96169935586363</v>
+        <v>23.89763389443656</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.536199537697239</v>
+        <v>0.5273457793361742</v>
       </c>
       <c r="C17" t="n">
-        <v>9.464342393250526</v>
+        <v>12.30305606260314</v>
       </c>
       <c r="D17" t="n">
-        <v>7.30113986675902</v>
+        <v>5.286672117460904</v>
       </c>
       <c r="E17" t="n">
-        <v>18.30168179770678</v>
+        <v>18.11707395940022</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.753970813453267</v>
+        <v>0.4152694614193584</v>
       </c>
       <c r="C18" t="n">
-        <v>11.00445910428771</v>
+        <v>11.22084611578075</v>
       </c>
       <c r="D18" t="n">
-        <v>7.815497123968009</v>
+        <v>4.785450644534738</v>
       </c>
       <c r="E18" t="n">
-        <v>20.57392704170899</v>
+        <v>16.42156622173485</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.760479800732423</v>
+        <v>0.4791419670576558</v>
       </c>
       <c r="C19" t="n">
-        <v>11.73501684092593</v>
+        <v>13.79985806492895</v>
       </c>
       <c r="D19" t="n">
-        <v>7.964919124554373</v>
+        <v>5.22798323970103</v>
       </c>
       <c r="E19" t="n">
-        <v>21.46041576621273</v>
+        <v>19.50698327168764</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1.962818002577691</v>
+        <v>0.5408938976547802</v>
       </c>
       <c r="C20" t="n">
-        <v>13.44759717116815</v>
+        <v>16.4126323176262</v>
       </c>
       <c r="D20" t="n">
-        <v>8.469753429032169</v>
+        <v>5.619091890118875</v>
       </c>
       <c r="E20" t="n">
-        <v>23.88016860277801</v>
+        <v>22.57261810539985</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.169477500252885</v>
+        <v>0.5908844907550278</v>
       </c>
       <c r="C21" t="n">
-        <v>9.847096370705231</v>
+        <v>19.05196284572332</v>
       </c>
       <c r="D21" t="n">
-        <v>7.095561897489739</v>
+        <v>5.973011937499849</v>
       </c>
       <c r="E21" t="n">
-        <v>18.11213576844785</v>
+        <v>25.6158592739782</v>
       </c>
     </row>
   </sheetData>
